--- a/Employee_Reports_wi48/Lorence Cardenas Cabales Q0614.xlsx
+++ b/Employee_Reports_wi48/Lorence Cardenas Cabales Q0614.xlsx
@@ -560,11 +560,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -609,11 +609,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -658,11 +658,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -707,11 +707,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -756,11 +756,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -805,11 +805,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -854,11 +854,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -903,11 +903,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -952,11 +952,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1001,11 +1001,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1050,11 +1050,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1099,11 +1099,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1148,11 +1148,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1197,11 +1197,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1246,11 +1246,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1283,11 +1283,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1332,11 +1332,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1381,11 +1381,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1431,11 +1431,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1480,11 +1480,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1517,11 +1517,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1554,11 +1554,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1603,11 +1603,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1652,11 +1652,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1701,11 +1701,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1750,11 +1750,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1787,11 +1787,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1824,11 +1824,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1861,11 +1861,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1898,11 +1898,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -1935,11 +1935,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -1984,11 +1984,11 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7846</v>
+        <v>7843</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
